--- a/MIS/public/templateJS.xlsx
+++ b/MIS/public/templateJS.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ad PROJECT\MIS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B2DE2A-7B5B-4F58-B782-AD9DE88F19F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87480FA4-6B9F-4370-96AA-73B1233A640D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>HELPDESK / SERVICE JOBSHEET</t>
   </si>
@@ -84,23 +95,7 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Part no</t>
-  </si>
-  <si>
-    <t>Keyboard</t>
-  </si>
-  <si>
-    <t>Job Sheet Status</t>
-  </si>
-  <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Follow 
-up Date</t>
-  </si>
-  <si>
-    <t>AgreedBy</t>
   </si>
   <si>
     <t>Raised By:</t>
@@ -181,7 +176,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -190,118 +185,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -311,35 +194,165 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -349,8 +362,27 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -360,132 +392,122 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -769,7 +791,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" customWidth="1"/>
@@ -779,34 +801,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="A1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="28"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="30"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -816,371 +838,330 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22"/>
-      <c r="F4" s="7" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="J4" s="22"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="22"/>
-      <c r="F6" s="7" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="11"/>
+      <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="22"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="11"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="22"/>
-      <c r="F8" s="7" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="F8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="22"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="11"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="22"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="G10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="17"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="20"/>
     </row>
     <row r="13" spans="1:10" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="15" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="16" t="s">
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="33"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="26"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="34"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="35"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="36"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="28"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="34"/>
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="36"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="28"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="34"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="36"/>
+      <c r="A18" s="27"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="35"/>
-      <c r="F19" s="35"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="36"/>
+      <c r="A19" s="27"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="36"/>
+      <c r="A20" s="27"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="36"/>
+      <c r="A21" s="27"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="36"/>
+      <c r="A22" s="27"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="28"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="39"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="31"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="14"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="34"/>
     </row>
     <row r="26" spans="1:10" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H27" s="8" t="s">
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="38" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="40">
+      <c r="A28" s="39">
         <v>1</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="40"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="40">
+        <f>H28*I28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="44"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
+      <c r="B32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4"/>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="14"/>
-    </row>
-    <row r="31" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="B35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4"/>
+    </row>
+    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J31" s="11" t="s">
+      <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-    </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
+      <c r="A39" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="23">
+    <mergeCell ref="B28:G28"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B35:E35"/>
     <mergeCell ref="G6:J6"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="B10:E10"/>
@@ -1193,12 +1174,7 @@
     <mergeCell ref="D15:G23"/>
     <mergeCell ref="H15:J23"/>
     <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="B31:H31"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B27:G27"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>

--- a/MIS/public/templateJS.xlsx
+++ b/MIS/public/templateJS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ad PROJECT\MIS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87480FA4-6B9F-4370-96AA-73B1233A640D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C0DB54-52ED-48C1-B23D-B29867127383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -404,111 +404,111 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -801,18 +801,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -826,9 +826,9 @@
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="14"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -846,58 +846,58 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
       <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="14"/>
       <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="11"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="14"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
       <c r="F8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="11"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
       <c r="G10" s="4" t="s">
         <v>19</v>
       </c>
@@ -953,152 +953,186 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="27"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="27"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="29"/>
       <c r="H16" s="27"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="27"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="27"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="27"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="29"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="27"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="27"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="29"/>
       <c r="H18" s="27"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="29"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="27"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
       <c r="D19" s="27"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="29"/>
       <c r="H19" s="27"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="29"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="27"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="27"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="29"/>
       <c r="H20" s="27"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="29"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="27"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
       <c r="D21" s="27"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="29"/>
       <c r="H21" s="27"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="29"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="27"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="29"/>
       <c r="H22" s="27"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="31"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="32"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="34"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="35"/>
     </row>
     <row r="26" spans="1:10" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38" t="s">
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="I27" s="38" t="s">
+      <c r="I27" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J27" s="38" t="s">
+      <c r="J27" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="39">
+      <c r="A28" s="6">
         <v>1</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40">
+      <c r="B28" s="8"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7">
         <f>H28*I28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>2</v>
+      </c>
+      <c r="B29" s="8"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7">
+        <f>H29*I29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>3</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7">
+        <f>H30*I30</f>
         <v>0</v>
       </c>
     </row>
@@ -1106,12 +1140,12 @@
       <c r="A32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
@@ -1123,12 +1157,12 @@
       <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
@@ -1140,18 +1174,20 @@
       <c r="A38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="25">
+    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:G28"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="H2:J2"/>
@@ -1159,22 +1195,22 @@
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="D14:G14"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="A15:C23"/>
     <mergeCell ref="D15:G23"/>
     <mergeCell ref="H15:J23"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B35:E35"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>

--- a/MIS/public/templateJS.xlsx
+++ b/MIS/public/templateJS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ad PROJECT\MIS\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C0DB54-52ED-48C1-B23D-B29867127383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3796AF2D-0066-48BD-B339-35AC26C20277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>HELPDESK / SERVICE JOBSHEET</t>
   </si>
@@ -131,12 +131,18 @@
       <t>SDLIT010 V7</t>
     </r>
   </si>
+  <si>
+    <t>Raised date:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$]d\ mmmm\,\ yyyy;@" x16r2:formatCode16="[$-en-BD,1]d\ mmmm\,\ yyyy;@"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,6 +173,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -392,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -411,6 +426,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -420,95 +453,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -801,18 +822,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -826,9 +847,9 @@
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="10"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
@@ -846,235 +867,235 @@
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="14"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="21"/>
       <c r="F4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="21"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21"/>
       <c r="F6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="14"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="21"/>
       <c r="F8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="14"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
       <c r="G10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="17"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="36"/>
     </row>
     <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="20"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39"/>
     </row>
     <row r="13" spans="1:10" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="21" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="21" t="s">
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="24"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="26"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="27"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="27"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="29"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="29"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="30"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="27"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="29"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="27"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="29"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="30"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="27"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="29"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="30"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="29"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="30"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="27"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="29"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="30"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="32"/>
+      <c r="A23" s="31"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="33"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="35"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" ht="5.0999999999999996" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="38"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="13"/>
       <c r="H27" s="5" t="s">
         <v>18</v>
       </c>
@@ -1089,12 +1110,12 @@
       <c r="A28" s="6">
         <v>1</v>
       </c>
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="10"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="16"/>
       <c r="H28" s="7"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7">
@@ -1106,12 +1127,12 @@
       <c r="A29" s="6">
         <v>2</v>
       </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="10"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="16"/>
       <c r="H29" s="7"/>
       <c r="I29" s="7"/>
       <c r="J29" s="7">
@@ -1123,12 +1144,12 @@
       <c r="A30" s="6">
         <v>3</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="10"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="16"/>
       <c r="H30" s="7"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7">
@@ -1140,52 +1161,72 @@
       <c r="A32" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
     </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
     </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="40"/>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="G38" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="41"/>
+      <c r="I38" s="42">
+        <f ca="1">TODAY()</f>
+        <v>46247</v>
+      </c>
+      <c r="J38" s="42"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="27">
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="B29:G29"/>
     <mergeCell ref="A25:J25"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:G28"/>
@@ -1202,15 +1243,6 @@
     <mergeCell ref="D15:G23"/>
     <mergeCell ref="H15:J23"/>
     <mergeCell ref="G6:J6"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B35:E35"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
